--- a/data/持倉月度追蹤.xlsx
+++ b/data/持倉月度追蹤.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+7% / +8% / +13% / +11% / +10% / +9%</t>
+          <t>+8% / +13% / +11% / +10% / +9% / +8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5% / +5% / +5% / +6% / +8% / +5%</t>
+          <t>+5% / +5% / +6% / +8% / +5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-7% / +8% / +15% / +29% / +16% / +18%</t>
+          <t>+8% / +15% / +29% / +16% / +18% / +16%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -618,12 +618,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>⚠️ 警示</t>
+          <t>✓ 正常</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+9% / +4% / +1% / +12% / -15% / -12%</t>
+          <t>+4% / +1% / +12% / -15% / -12% / +29%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>⚠️ 最新月 YoY -11.6% ≤ -8%</t>
+          <t>持續觀察</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+21% / +17% / +19% / +8% / +19% / +10%</t>
+          <t>+17% / +19% / +8% / +19% / +10% / +16%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+22% / +15% / +15% / +19% / +32% / +26%</t>
+          <t>+15% / +15% / +19% / +32% / +26% / +16%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1% / +2% / +11% / +1% / +6% / +16%</t>
+          <t>+2% / +11% / +1% / +6% / +16% / +1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+29% / +37% / +40% / +27% / +34% / +24%</t>
+          <t>+37% / +40% / +27% / +34% / +24% / +19%</t>
         </is>
       </c>
       <c r="F9" t="n">
